--- a/artfynd/A 3006-2026 artfynd.xlsx
+++ b/artfynd/A 3006-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118835345</v>
+        <v>118834853</v>
       </c>
       <c r="B2" t="n">
-        <v>57995</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532203</v>
+        <v>532204</v>
       </c>
       <c r="R2" t="n">
-        <v>6545935</v>
+        <v>6545954</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>04:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>04:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +784,613 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Ola Erlandsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118834757</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57942</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Solberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>532302</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6545981</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Sara Poppelaars</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118834427</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Solberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532306</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6545970</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ola Erlandsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118835404</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Solberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>532264</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6546015</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ola Erlandsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118835345</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Solberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532203</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6545935</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118834886</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Solberga, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>532271</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6545897</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>04:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>04:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Alight - Brevens bruk</t>
         </is>

--- a/artfynd/A 3006-2026 artfynd.xlsx
+++ b/artfynd/A 3006-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834853</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118835404</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118835345</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1395,8 +1425,21 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>